--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0218.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0218.xlsx
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>R?i ?i!</t>
+          <t>Rời đi!</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>R?i ?i!</t>
+          <t>Rời đi!</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Sanhua trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Sanhua trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Baizhi hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Baizhi hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Chixia hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Chixia hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Chixia hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Chixia hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Mortefi hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Mortefi hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Yinlin trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yinlin trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Yuanwu trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yuanwu trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Yangyang trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yangyang trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Yangyang trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Yangyang trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Aalto hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Aalto hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Jiyan hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Jiyan hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Jiyan hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Jiyan hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Jianxin hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Jianxin hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Verina trợ chiến.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Verina trợ chiến.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Companion's Aid]&lt;/color&gt; Triệu hồi Danjin hỗ trợ.</t>
+          <t>&lt;color=#ffd12f&gt;[Hỗ Trợ Đồng Hành]&lt;/color&gt; Triệu hồi Danjin hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Kháng Đứt Tác Động được tăng mạnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Kháng Đứt Tác Động được tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Kháng Đứt Tác Động được tăng mạnh.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Kháng Đứt Tác Động được tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -30085,7 +30085,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
 Nhận toàn bộ hiệu ứng của [Sức Mạnh Cảnh Mơ] ngoại trừ [Kỵ Sĩ Thời Gian].</t>
         </is>
       </c>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Lucid Dream]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Giấc Mơ Tỉnh]&lt;/color&gt;
 Nhận toàn bộ hiệu ứng của [Sức Mạnh Cảnh Mơ] ngoại trừ [Kỵ Sĩ Thời Gian].</t>
         </is>
       </c>
@@ -30219,7 +30219,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi không kích hoạt hiệu ứng [Sức Mạnh Giấc Mơ] nào trong 4 giây, tốc độ hồi [Năng Lượng Giấc Mơ] tăng gấp đôi.</t>
         </is>
       </c>
@@ -30286,7 +30286,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Energy]&lt;/color&gt;
+          <t>&lt;color=#ffd12f&gt;[Năng Lượng Giấc Mơ]&lt;/color&gt;
 Khi không kích hoạt hiệu ứng [Sức Mạnh Giấc Mơ] nào trong một khoảng thời gian ngắn, tốc độ hồi [Năng Lượng Giấc Mơ] tăng gấp đôi.</t>
         </is>
       </c>
@@ -30353,8 +30353,8 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;[Time Rider]&lt;/color&gt;, tốc độ sinh Năng Lượng Thời Gian tăng gấp ba lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;[Kỵ Sĩ Thời Gian]&lt;/color&gt;, tốc độ sinh Năng Lượng Thời Gian tăng gấp ba lần.</t>
         </is>
       </c>
     </row>
@@ -30420,8 +30420,8 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Dreamscape Power Enhancement]&lt;/color&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;Time Rider&lt;/color&gt;, tốc độ sinh Năng Lượng Thời Gian tăng gấp ba lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Cường Sức Mạnh Giấc Mơ]&lt;/color&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;Kỵ Sĩ Thời Gian&lt;/color&gt;, tốc độ sinh Năng Lượng Thời Gian tăng gấp ba lần.</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên sau khi né thành công.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên sau khi né thành công.</t>
         </is>
       </c>
     </row>
@@ -30551,7 +30551,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên khi bị tấn công.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên khi bị tấn công.</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Hiệu ứng "Chuông Băng" kích hoạt khi bị tấn công nếu đang có khiên.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Hiệu ứng "Chuông Băng" kích hoạt khi bị tấn công nếu đang có khiên.</t>
         </is>
       </c>
     </row>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Fusion".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Fusion".</t>
         </is>
       </c>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Fusion".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Fusion".</t>
         </is>
       </c>
     </row>
@@ -30941,7 +30941,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Electro".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Electro".</t>
         </is>
       </c>
     </row>
@@ -31006,7 +31006,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Electro".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Electro".</t>
         </is>
       </c>
     </row>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Aero".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Aero".</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Metaphor]&lt;/color&gt; Nhận ba "Aero".</t>
+          <t>&lt;color=#ffd12f&gt;[Ẩn Dụ]&lt;/color&gt; Nhận ba "Aero".</t>
         </is>
       </c>
     </row>
